--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evolution-effet-indesirable.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evolution-effet-indesirable.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3544,7 +3544,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>146</v>
       </c>
@@ -3559,13 +3559,13 @@
         <v>62</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3647,7 +3647,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>150</v>
       </c>
@@ -3662,13 +3662,13 @@
         <v>151</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3956,7 +3956,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>164</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evolution-effet-indesirable.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evolution-effet-indesirable.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
